--- a/excel/JUNIORS report templates.xlsx
+++ b/excel/JUNIORS report templates.xlsx
@@ -3,10 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="3D_ANIMATOR" sheetId="1" r:id="rId1"/>
-    <sheet name="WEBSITE_DESIGNER" sheetId="2" r:id="rId2"/>
-    <sheet name="VIRTUAL_WORLD_MAKER" sheetId="3" r:id="rId3"/>
-    <sheet name="LITTLE_PROGRAMMER" sheetId="4" r:id="rId4"/>
+    <sheet name="VIRTUAL_WORLD_MAKER" sheetId="1" r:id="rId1"/>
+    <sheet name="LITTLE_PROGRAMMER" sheetId="2" r:id="rId2"/>
+    <sheet name="3D_ANIMATOR" sheetId="3" r:id="rId3"/>
+    <sheet name="WEBSITE_DESIGNER" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -400,638 +400,562 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>VIRTUAL WORLD MAKER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3D ANIMATOR 1</v>
-      </c>
-      <c r="H3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="I3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="F4" t="str">
-        <v>A</v>
-      </c>
-      <c r="G4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="F5" t="str">
-        <v>B</v>
-      </c>
-      <c r="G5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa mengingat dan memahami kembali konsep dasar coding dengan [sangat baik/ baik/ cukup baik], yaitu algoritma, event, loop, dan conditional (code If). [NAMA_STUDENT] juga mempelajari literasi digital seperti pengaruh screen time &amp; gadget addiction, cara mencegah cyber bullying, media balance, dan perbedaan komunikasi langsung dengan online. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="F6" t="str">
-        <v>C</v>
-      </c>
-      <c r="G6" t="str">
-        <v>cukup baik</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-[NAMA_STUDENT]  menunjukkan kemajuan yang [sangat baik/ baik/ cukup baik]. dalam belajar Coding_x000d_
-untuk pertama kalinya. [NAMA_STUDENT]  mulai memahami konsep dasar_x000d_
-komputer seperti mouse, keyboard dan layar dan_x000d_
-menggunakannya secara sederhana untuk navigasi dan input._x000d_
-[NAMA_STUDENT]  juga memahami literasi digital dengan [sangat baik/ baik/ cukup baik]. seperti_x000d_
-pentingnya media balance dan mencegah cyber bullying. Good_x000d_
-Job [NAMA_STUDENT] !</v>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dengan [sangat baik/ baik/ cukup baik], mulai dari membuat animasi dan menggerakkan karakter dengan code If di Scratch, memprogram robot dengan platform baru, hingga mengenal dan mengendalikan Drone secara virtual. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] bisa memahami konsep dasar seperti algoritma dan blok
-kode, dan mampu membuat animasi dasar dengan ScratchJr.
-Selain itu, [NAMA_STUDENT] mulai terbiasa menggunakan aplikasi Wonder
-untuk mendukung proses belajarnya. Ini menunjukkan
-kemampuannya berkembang dalam memanfaatkan teknologi
-digital untuk memperluas pengetahuannya. Good Job [NAMA_STUDENT]!
-</v>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Character</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B16" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusia] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu
-yang [tinggi/ cukup tinggi] sehingga [mudah/kadang] terdistraksi dengan hal yang lain.
-Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal
-yang tidak diketahui dan juga menyampaikan pendapat di
-dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>VIRTUAL WORLD MAKER 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3D ANIMATOR 2</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengingat kembali dan memahami konsep coding dengan [sangat baik/ baik/ cukup baik], yaitu conditional (bug &amp; debugging), function, conditional loop, dan forever loop. [NAMA_STUDENT] juga mempelajari literasi digital seperti pentingnya menghargai copyright, cara mengenali dan menghindari spam, serta pentingnya tetap berusaha dan pantang menyerah. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] terhadap
-literasi digital, dasar penggunaan komputer seperti keyboard
-dan mouse.[NAMA_STUDENT] juga cukup memahami coding konsep seperti
-conditional, debugging, dan animasi sederhana. Tetap
-semangat ya [NAMA_STUDENT]!
-</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat Bug Hunter Game dan Beetle Race Game di Scratch menggunakan kode Glide, mengaplikasikan function pada coding game dan robot, serta memprogram Micro:bit dengan kode Forever. Nice work [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B29" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C29" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="D29" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] bisa menyusun blok coding dengan [sangat baik/ baik/ cukup baik] di Scratch
-Junior, memberi instruksi pada Cue robot dan membuat animasi
-sederhana di scratch dan animasi
-3D di Kodu. Namun, [NAMA_STUDENT] masih membutuhkan perhatian khusus
-agar bisa fokus mengerjakan latihan coding.
-Keep it up [NAMA_STUDENT]!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>3D ANIMATOR 3</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B37" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C37" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] telah menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] dalam
-mengenali gambar atau video palsu. [NAMA_STUDENT], Arka masih
-membutuhkan bimbingan dalam memahami cara yang benar
-untuk mendownload dan mengupload konten dengan hak cipta.
-[NAMA_STUDENT] juga semakin mahir dalam menggunakan dasar-dasar
-komputer seperti keyboard dan mouse. Tetap semangat, [NAMA_STUDENT]!</v>
+        <v>VIRTUAL WORLD MAKER 3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan, yaitu function, variable, dan operator. [NAMA_STUDENT] juga mempelajari literasi digital seperti perkembangan teknologi dalam kehidupan manusia serta cara mengenali dan menghindari hoax. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B42" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C42" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="D42" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Arka masih membutuhkan bimbingan dalam menggunakan_x000d_
-platform Kodu untuk membuat game 3D seperti underwater_x000d_
-game dan cycle race. Selain itu, Arka juga belum sepenuhnya_x000d_
-memahami konsep conditional loop. Tapi jika dibimbing teacher,_x000d_
-Arka dapat lebih fokus dan menunjukkan kemampuan coding_x000d_
-yang semakin berkembang. Keep it up, Arka! You're doing great.</v>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding pada project Virtual Reality dengan [sangat baik/ baik/ cukup baik], mulai dari membuat VR pameran hewan dan VR "Finding Animal" menggunakan function, VR City Tour, Math Game dengan operator, hingga multiple diorama VR dan project akhir Solar System VR yang dipresentasikan dengan baik. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>LITTLE PROGRAMMER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Website Designer 1</v>
-      </c>
-      <c r="H3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="I3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="F4" t="str">
-        <v>A</v>
-      </c>
-      <c r="G4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="F5" t="str">
-        <v>B</v>
-      </c>
-      <c r="G5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa memahami konsep coding dasar dengan [sangat baik/ baik/ cukup baik], yaitu variable, list, dan broadcast. [NAMA_STUDENT] juga mempelajari literasi digital seperti Cloud Storage, Internet of Things (IoT) untuk membantu kehidupan sehari-hari, jejak digital, komunitas online dan perkembangannya, serta virus komputer dan cara mengatasinya. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="F6" t="str">
-        <v>C</v>
-      </c>
-      <c r="G6" t="str">
-        <v>cukup baik</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Gavin meningkatkan keterampilan motorik halusnya dengan berlatih mengoperasikan komputer, termasuk mengetik, mengklik, dan drag mouse dengan menggunakan berbagai platform coding. Dia menunjukkan pemahaman yang sangat baik di bidang konsep komputer dan literasi digital. Ia juga mampu menguasai materi dengan cepat . Ke depannya, Gavin bisa meningkatkan fokus pada detail untuk memperkuat kemampuan analisisnya.</v>
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dengan [sangat baik/ baik/ cukup baik], mulai dari mengaplikasikan variable pada Micro:bit, membuat animasi Greeting Card dengan kode Broadcast, mengkombinasikan robot Maqueen dengan Micro:bit, membuat animasi Lost in Space dan Flying Game di Scratch, hingga membuat game animasi menggunakan konsep List. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Gavin telah mempelajari dan menerapkan konsep coding seperti conditional loop dan function melalui game coding sederhana. Dia  juga telah mengeksplor cara menggunakan konsep-konsep tersebut untuk membuat animasi sederhana menggunakan telknologi  VR dan AR. Gavin sangat antusias belajar, namun perlu terus berlatih menyusun kode yang lebih kompleks agar lebih percaya diri.</v>
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Character</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B16" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusia] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu
-yang [tinggi/ cukup tinggi] sehingga [mudah/kadang] terdistraksi dengan hal yang lain.
-Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal
-yang tidak diketahui dan juga menyampaikan pendapat di
-dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Gavin sangat antusias setiap di kelas. Dia juga sangat fokus ketika mengerjakan latihan. Ketika ada yang bingung, Gavin selalu bertanya. Keep itu Gavin!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LITTLE PROGRAMMER 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Web Designer 2</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengingat kembali dan memahami konsep coding dengan [sangat baik/ baik/ cukup baik], yaitu clone dan wireless controller (koneksi antar device). [NAMA_STUDENT] juga mempelajari literasi digital seperti apa itu Operating System dan konsep Addictive Design pada game maupun aplikasi. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] terhadap
-literasi digital, dasar penggunaan komputer seperti keyboard
-dan mouse.[NAMA_STUDENT] juga cukup memahami coding konsep seperti
-conditional, debugging, dan animasi sederhana. Tetap
-semangat ya [NAMA_STUDENT]!
-</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding dan desain dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat quiz interaktif dan Augmented Reality (AR) tentang bangunan bersejarah di berbagai negara, coding Wireless Controller pada Micro:bit dan Maqueen, animasi Clone War di Scratch, serta mengerjakan project game "Create Your Own World" dari awal hingga bagian kedua. Nice work [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B29" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C29" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="D29" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] bisa menyusun blok coding dengan [sangat baik/ baik/ cukup baik] di Scratch
-Junior, memberi instruksi pada Cue robot dan membuat animasi
-sederhana di scratch dan animasi
-3D di Kodu. Namun, [NAMA_STUDENT] masih membutuhkan perhatian khusus
-agar bisa fokus mengerjakan latihan coding.
-Keep it up [NAMA_STUDENT]!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>3D ANIMATOR 3</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B37" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C37" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] telah menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] dalam
-mengenali gambar atau video palsu. [NAMA_STUDENT], Arka masih
-membutuhkan bimbingan dalam memahami cara yang benar
-untuk mendownload dan mengupload konten dengan hak cipta.
-[NAMA_STUDENT] juga semakin mahir dalam menggunakan dasar-dasar
-komputer seperti keyboard dan mouse. Tetap semangat, [NAMA_STUDENT]!</v>
+        <v>LITTLE PROGRAMMER 3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan, yaitu text coding dengan bahasa Python serta penerapan operator dan variable pada robot. [NAMA_STUDENT] juga mempelajari literasi digital seperti pengenalan kecerdasan buatan (AI) dan internet sebagai sumber informasi dan tempat belajar. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B42" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C42" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="D42" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Arka masih membutuhkan bimbingan dalam menggunakan_x000d_
-platform Kodu untuk membuat game 3D seperti underwater_x000d_
-game dan cycle race. Selain itu, Arka juga belum sepenuhnya_x000d_
-memahami konsep conditional loop. Tapi jika dibimbing teacher,_x000d_
-Arka dapat lebih fokus dan menunjukkan kemampuan coding_x000d_
-yang semakin berkembang. Keep it up, Arka! You're doing great.</v>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk membuat project game sendiri. [NAMA_STUDENT] membuat Soccer Game di Scratch, menentukan ide dan mengumpulkan asset, menyusun layout, coding logic permainan (life, score, dan next level), hingga launch game dan mempersiapkan presentasi. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1042,7 +966,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>VIRTUAL WORLD MAKER 1</v>
+        <v>3D ANIMATOR 1</v>
       </c>
     </row>
     <row r="2">
@@ -1060,9 +984,16 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>[NAMA_STUDENT] bisa mengingat dan memahami kembali konsep dasar coding dengan [sangat baik/ baik/ cukup baik], yaitu algoritma, event, loop, dan conditional (code If). [NAMA_STUDENT] juga mempelajari literasi digital seperti pengaruh screen time &amp; gadget addiction, cara mencegah cyber bullying, media balance, dan perbedaan komunikasi langsung dengan online. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+[NAMA_STUDENT]  menunjukkan kemajuan yang [sangat baik/ baik/ cukup baik]. dalam belajar Coding_x000d_
+untuk pertama kalinya. [NAMA_STUDENT]  mulai memahami konsep dasar_x000d_
+komputer seperti mouse, keyboard dan layar dan_x000d_
+menggunakannya secara sederhana untuk navigasi dan input._x000d_
+[NAMA_STUDENT]  juga memahami literasi digital dengan [sangat baik/ baik/ cukup baik]. seperti_x000d_
+pentingnya media balance dan mencegah cyber bullying. Good_x000d_
+Job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
@@ -1085,9 +1016,15 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dengan [sangat baik/ baik/ cukup baik], mulai dari membuat animasi dan menggerakkan karakter dengan code If di Scratch, memprogram robot dengan platform baru, hingga mengenal dan mengendalikan Drone secara virtual. Good job [NAMA_STUDENT] !</v>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] bisa memahami konsep dasar seperti algoritma dan blok
+kode, dan mampu membuat animasi dasar dengan ScratchJr.
+Selain itu, [NAMA_STUDENT] mulai terbiasa menggunakan aplikasi Wonder
+untuk mendukung proses belajarnya. Ini menunjukkan
+kemampuannya berkembang dalam memanfaatkan teknologi
+digital untuk memperluas pengetahuannya. Good Job [NAMA_STUDENT]!
+</v>
       </c>
     </row>
     <row r="11">
@@ -1112,7 +1049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="16">
@@ -1132,7 +1069,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>VIRTUAL WORLD MAKER 2</v>
+        <v>3D ANIMATOR 2</v>
       </c>
     </row>
     <row r="20">
@@ -1150,9 +1087,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>[NAMA_STUDENT] bisa mengingat kembali dan memahami konsep coding dengan [sangat baik/ baik/ cukup baik], yaitu conditional (bug &amp; debugging), function, conditional loop, dan forever loop. [NAMA_STUDENT] juga mempelajari literasi digital seperti pentingnya menghargai copyright, cara mengenali dan menghindari spam, serta pentingnya tetap berusaha dan pantang menyerah. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] terhadap
+literasi digital, dasar penggunaan komputer seperti keyboard
+dan mouse.[NAMA_STUDENT] juga cukup memahami coding konsep seperti
+conditional, debugging, dan animasi sederhana. Tetap
+semangat ya [NAMA_STUDENT]!
+</v>
       </c>
     </row>
     <row r="24">
@@ -1175,9 +1117,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>[NAMA_STUDENT] bisa menerapkan konsep coding yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat Bug Hunter Game dan Beetle Race Game di Scratch menggunakan kode Glide, mengaplikasikan function pada coding game dan robot, serta memprogram Micro:bit dengan kode Forever. Nice work [NAMA_STUDENT] !</v>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] bisa menyusun blok coding dengan [sangat baik/ baik/ cukup baik] di Scratch
+Junior, memberi instruksi pada Cue robot dan membuat animasi
+sederhana di scratch dan animasi
+3D di Kodu. Namun, [NAMA_STUDENT] masih membutuhkan perhatian khusus
+agar bisa fokus mengerjakan latihan coding.
+Keep it up [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="29">
@@ -1202,7 +1149,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="34">
@@ -1222,7 +1169,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>VIRTUAL WORLD MAKER 3</v>
+        <v>3D ANIMATOR 3</v>
       </c>
     </row>
     <row r="38">
@@ -1240,9 +1187,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan, yaitu function, variable, dan operator. [NAMA_STUDENT] juga mempelajari literasi digital seperti perkembangan teknologi dalam kehidupan manusia serta cara mengenali dan menghindari hoax. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] telah menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] dalam
+mengenali gambar atau video palsu. [NAMA_STUDENT] masih
+membutuhkan bimbingan dalam memahami cara yang benar
+untuk mendownload dan mengupload konten dengan hak cipta.
+[NAMA_STUDENT] juga semakin mahir dalam menggunakan dasar-dasar
+komputer seperti keyboard dan mouse. Tetap semangat, [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="42">
@@ -1267,7 +1219,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>[NAMA_STUDENT] bisa menerapkan konsep coding pada project Virtual Reality dengan [sangat baik/ baik/ cukup baik], mulai dari membuat VR pameran hewan dan VR "Finding Animal" menggunakan function, VR City Tour, Math Game dengan operator, hingga multiple diorama VR dan project akhir Solar System VR yang dipresentasikan dengan baik. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] masih membutuhkan bimbingan dalam menggunakan platform Kodu untuk membuat game 3D seperti underwater game dan cycle race. Selain itu, [NAMA_STUDENT] juga belum sepenuhnya memahami konsep conditional loop. Namun jika dibimbing teacher, [NAMA_STUDENT] bisa lebih fokus dan menunjukkan kemampuan coding yang semakin berkembang. Keep it up, [NAMA_STUDENT]! You're doing great.</v>
       </c>
     </row>
     <row r="47">
@@ -1292,7 +1244,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="52">
@@ -1323,7 +1275,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>LITTLE PROGRAMMER 1</v>
+        <v>WEBSITE DESIGNER 1</v>
       </c>
     </row>
     <row r="2">
@@ -1343,7 +1295,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>[NAMA_STUDENT] bisa memahami konsep coding dasar dengan [sangat baik/ baik/ cukup baik], yaitu variable, list, dan broadcast. [NAMA_STUDENT] juga mempelajari literasi digital seperti Cloud Storage, Internet of Things (IoT) untuk membantu kehidupan sehari-hari, jejak digital, komunitas online dan perkembangannya, serta virus komputer dan cara mengatasinya. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] meningkatkan keterampilan motorik halusnya dengan [sangat baik/ baik/ cukup baik], berlatih mengoperasikan komputer termasuk mengetik, mengklik, dan drag mouse menggunakan berbagai platform coding. [NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] di bidang konsep komputer dan literasi digital serta mampu menguasai materi dengan cepat. Ke depannya, [NAMA_STUDENT] bisa meningkatkan fokus pada detail untuk memperkuat kemampuan analisisnya. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
@@ -1368,7 +1320,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dengan [sangat baik/ baik/ cukup baik], mulai dari mengaplikasikan variable pada Micro:bit, membuat animasi Greeting Card dengan kode Broadcast, mengkombinasikan robot Maqueen dengan Micro:bit, membuat animasi Lost in Space dan Flying Game di Scratch, hingga membuat game animasi menggunakan konsep List. Good job [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa mempelajari dan menerapkan konsep coding seperti conditional loop dan function dengan [sangat baik/ baik/ cukup baik] melalui game coding sederhana. [NAMA_STUDENT] juga mengeksplorasi cara menggunakan konsep-konsep tersebut untuk membuat animasi sederhana menggunakan teknologi VR dan AR. [NAMA_STUDENT] sangat antusias belajar, namun perlu terus berlatih menyusun kode yang lebih kompleks agar lebih percaya diri. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
@@ -1393,7 +1345,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="16">
@@ -1413,7 +1365,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>LITTLE PROGRAMMER 2</v>
+        <v>WEBSITE DESIGNER 2</v>
       </c>
     </row>
     <row r="20">
@@ -1431,9 +1383,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>[NAMA_STUDENT] bisa mengingat kembali dan memahami konsep coding dengan [sangat baik/ baik/ cukup baik], yaitu clone dan wireless controller (koneksi antar device). [NAMA_STUDENT] juga mempelajari literasi digital seperti apa itu Operating System dan konsep Addictive Design pada game maupun aplikasi. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] terhadap
+literasi digital, dasar penggunaan komputer seperti keyboard
+dan mouse.[NAMA_STUDENT] juga cukup memahami coding konsep seperti
+conditional, debugging, dan animasi sederhana. Tetap
+semangat ya [NAMA_STUDENT]!
+</v>
       </c>
     </row>
     <row r="24">
@@ -1456,9 +1413,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>[NAMA_STUDENT] bisa menerapkan konsep coding dan desain dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat quiz interaktif dan Augmented Reality (AR) tentang bangunan bersejarah di berbagai negara, coding Wireless Controller pada Micro:bit dan Maqueen, animasi Clone War di Scratch, serta mengerjakan project game "Create Your Own World" dari awal hingga bagian kedua. Nice work [NAMA_STUDENT] !</v>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] bisa menyusun blok coding dengan [sangat baik/ baik/ cukup baik] di Scratch
+Junior, memberi instruksi pada Cue robot dan membuat animasi
+sederhana di scratch dan animasi
+3D di Kodu. Namun, [NAMA_STUDENT] masih membutuhkan perhatian khusus
+agar bisa fokus mengerjakan latihan coding.
+Keep it up [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="29">
@@ -1483,7 +1445,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="34">
@@ -1503,7 +1465,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LITTLE PROGRAMMER 3</v>
+        <v>WEBSITE DESIGNER 3</v>
       </c>
     </row>
     <row r="38">
@@ -1521,9 +1483,14 @@
         <v>VARIASI 1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan, yaitu text coding dengan bahasa Python serta penerapan operator dan variable pada robot. [NAMA_STUDENT] juga mempelajari literasi digital seperti pengenalan kecerdasan buatan (AI) dan internet sebagai sumber informasi dan tempat belajar. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str" xml:space="preserve">
+        <v xml:space="preserve">[NAMA_STUDENT] telah menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] dalam
+mengenali gambar atau video palsu. [NAMA_STUDENT] masih
+membutuhkan bimbingan dalam memahami cara yang benar
+untuk mendownload dan mengupload konten dengan hak cipta.
+[NAMA_STUDENT] juga semakin mahir dalam menggunakan dasar-dasar
+komputer seperti keyboard dan mouse. Tetap semangat, [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="42">
@@ -1548,7 +1515,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>[NAMA_STUDENT] bisa menerapkan konsep coding yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk membuat project game sendiri. [NAMA_STUDENT] membuat Soccer Game di Scratch, menentukan ide dan mengumpulkan asset, menyusun layout, coding logic permainan (life, score, dan next level), hingga launch game dan mempersiapkan presentasi. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] masih membutuhkan bimbingan dalam menggunakan platform Kodu untuk membuat game 3D seperti underwater game dan cycle race. Selain itu, [NAMA_STUDENT] juga belum sepenuhnya memahami konsep conditional loop. Namun jika dibimbing teacher, [NAMA_STUDENT] bisa lebih fokus dan menunjukkan kemampuan coding yang semakin berkembang. Keep it up, [NAMA_STUDENT]! You're doing great.</v>
       </c>
     </row>
     <row r="47">
@@ -1573,7 +1540,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] [sangat antusias/ antusias/ cukup antusias] setiap di kelas. [NAMA_STUDENT] mempunyai rasa ingin tahu yang [tinggi/ cukup tinggi] sehingga [mudah/ kadang] terdistraksi dengan hal yang lain. Walaupun begitu, [NAMA_STUDENT] tidak ragu-ragu bertanya tentang hal-hal yang tidak diketahui dan juga menyampaikan pendapat di dalam kelas. Tetap semangat ya [NAMA_STUDENT]!</v>
       </c>
     </row>
     <row r="52">
